--- a/TAF_NPP/bootstrap/data/WGINORStrata.xlsx
+++ b/TAF_NPP/bootstrap/data/WGINORStrata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin/Documents/Work/divers/Conferences_and_workshops/ICES_expert_groups/WGINOR/WGINOR_Git/WGINOR/TAF_NPP/bootstrap/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin/Documents/Work/divers/Conferences_and_workshops/ICES_expert_groups/WGINOR/Polygons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0DE5BB-147D-8E43-B160-08F5AC86A471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A878DFF6-17D5-D143-8855-87186021CBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3920" yWindow="4180" windowWidth="28800" windowHeight="16520" xr2:uid="{EDFD86B5-99E4-7C4C-AEFC-C7C7A6FAA39F}"/>
+    <workbookView xWindow="7820" yWindow="620" windowWidth="20980" windowHeight="16420" activeTab="1" xr2:uid="{EDFD86B5-99E4-7C4C-AEFC-C7C7A6FAA39F}"/>
   </bookViews>
   <sheets>
     <sheet name="StrataSystem" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="348">
   <si>
     <t>Version</t>
   </si>
@@ -910,15 +910,9 @@
     <t>AW</t>
   </si>
   <si>
-    <t>POLYGON((-25.7999992370605  60.5,-24.8999996185303  60.7333335876465,-24.2333335876465  60.7666664123535,-23.7999992370605  60.7000007629395,-23.5  60.533332824707,-22.033332824707  61.1333351135254,-21.3333339691162  61.2000007629395,-21.1333332061768  61.3666648864746,-21.2666664123535  61.533332824707,-20.7000007629395  61.7666664123535,-20.2000007629395  61.6666679382324,-19.6000003814697  61.7333335876465,-18.966667175293  61.6666679382324,-18.966667175293  61.966667175293,-18.6666660308838  61.966667175293,-18.0666675567627  61.8666648864746,-17.6333332061768  62.0666656494141,-17.533332824707  62.3333320617676,-17  62.5999984741211,-16.6333332061768  62.5,-15.5666666030884  62.6333351135254,-15.2666664123535  62.7333335876465,-14.7666664123535  61.7666664123535,-14.3999996185303  61.5,-14.6000003814697  61.2999992370605,-15  60.2333335876465,-15.6666669845581  59.966667175293,-16.0666675567627  59.7999992370605,-16.5666675567627  59.8333320617676,-18.1333332061768  59.4000015258789,-19.466667175293  58.7999992370605,-19.7999992370605  58.533332824707,-20.7333335876465  57.1666679382324,-21.033332824707  57.0666656494141,-22.1000003814697  56.466667175293,-22.5666675567627  56.4000015258789,-23.1666660308838  55.9333343505859,-23.2999992370605  55.7999992370605,-22.466667175293  55.4333343505859,-21.8666667938232  55.4333343505859,-20.8666667938232  55.5999984741211,-20.1333332061768  55.1666679382324,-20.2999992370605  55.033332824707,-20.1666660308838  53.7666664123535,-19.8666667938232  53.7000007629395,-18.6666660308838  54.1333351135254,-18.1333332061768  54.2999992370605,-17.6666660308838  54.5,-17.3333339691162  54.5666656494141,-16.533332824707  55.0666656494141,-15.7333335876465  55.2333335876465,-15.0333337783813  55.533332824707,-14.1666669845581  56,-12.8666667938232  57,-11.7333335876465  57.2333335876465,-11.5333337783813  57.5999984741211,-11.1666669845581  58,-10.6666669845581  58.2333335876465,-10.0666666030884  58.0999984741211,-9.53333377838135  58.2000007629395,-8.80000019073486  58.2999992370605,-8.33333301544189  58.3666648864746,-7.69999980926514  58.6666679382324,-7.30000019073486  59.033332824707,-7.03333330154419  59.1666679382324,-6.53333330154419  59.3333320617676,-6.06666660308838  59.6333351135254,-5.43333339691162  59.7333335876465,-4.93333339691162  59.9000015258789,-4.36666679382324  60.0999984741211,-3.79999995231628  60.3333320617676,-3.33333325386047  60.3333320617676,-3.13333344459534  60.4333343505859,-2.43333339691162  60.8333320617676,-0.699999988079071  61.5999984741211,-0.300000011920929  61.6333351135254,0.133333340287209  61.7333335876465,0.699999988079071  61.5999984741211,1.16666662693024  61.7000007629395,3.570012946  62.704987054,5.072916666  63.141654839,5.324345937  63.27982073,5.764583334  63.651352689,5.580264779  63.748901887,5.871012258  64.08125,5.673693034  64.777859701,6.112449529  65.135416667,5.752158435  65.477083333,6.306249999  66.21252281,7.06875  66.601942223,8.008228204  66.81260513,8.927083334  67.329302251,10.239583332  68.009456131,12.09711365  68.623719685,11.8000001907349  68.8000030517578,11.1333332061768  68.6666641235352,9.86666679382324  68.4000015258789,8.86666679382324  67.9000015258789,8.60000038146973  67.9000015258789,8.30000019073486  67.7666702270508,7.76666688919067  67.9000015258789,7.30000019073486  68.2333297729492,6.46666669845581  68.2333297729492,5.76666688919067  68.2333297729492,5.23333311080933  68.4333343505859,4.56666660308838  68.2333297729492,3.83333325386047  68.3666687011719,3.20000004768372  68.3333358764648,1.96666669845581  67.8333358764648,1.515144101  67.800477996,1.5  67.466667175293,1.43333327770233  66.966667175293,1.79999995231628  66.5,2.29999995231628  66.1333312988281,2.06666660308838  65.966667175293,2.90000009536743  65.4333343505859,2.79999995231628  64.9000015258789,3.23333334922791  64.7666702270508,3.63333344459534  64.4333343505859,2.46666669845581  64.1333312988281,1.96666669845581  64.1666641235352,1.014696942  63.626922445,-0.533333361148834  63.4000015258789,-1.73333334922791  63.2666664123535,-2.36791519  63.040542854,-3.20000004768372  63.1333351135254,-4.081391907  62.976460057,-5.76666688919067  63.0666656494141,-5.83333349227905  63.2666664123535,-7.35416173934937  63.6875,-8.39999961853027  63.9333343505859,-10.2666664123535  64.033332824707,-11.4791612625122  64.5208358764648,-12.5333337783813  64.4333343505859,-12.7333335876465  64.2333297729492,-14.2666664123535  63.7333335876465,-15.4333333969116  63.466667175293,-16.2333335876465  63.3333320617676,-17.6333332061768  63.2999992370605,-18.8999996185303  63.2666664123535,-19.7000007629395  63.3666648864746,-20.2333335876465  63.2333335876465,-21.9333324432373  63.3333320617676,-22.466667175293  63.6666679382324,-23.0666675567627  63.2999992370605,-25.7999992370605  60.5))</t>
-  </si>
-  <si>
     <t>EIW</t>
   </si>
   <si>
-    <t>POLYGON((-7.103168115  65.283694796,-6.96666669845581  65.7666702270508,-7.40000009536743  66.0999984741211,-7.330920869  66.384246437,-7.63333320617676  67,-7.519915283  67.25104165,-7.643573575  67.771548904,-7.16666650772095  68.033332824707,-6.93333339691162  68.3666687011719,-7.40000009536743  68.6333312988281,-7.848642619  68.677507828,-7.628274775  68.88475312,-7.561650198  69.247807348,-7.46864723  69.504553404,-7.346337391  69.867374303,-7.167894825  70.118813088,-6.897805367  70.446951911,-6.618760544  70.650056588,-6.173734426  70.746620275,-6.070436289  70.796587087,-6.482534667  70.877686691,-6.968045263  70.957275316,-7.329200449  71.01525725,-7.754596142  71.083122574,-8.283196925  71.153799736,-9.336997827  71.323403555,-10.543476003  71.485203733,-10.770921247  71.510746581,-10.978849338  71.521918122,-11.279133026  71.268840323,-11.787762901  70.977924869,-12.164007593  70.696499491,-12.661247931  70.313189626,-13.025778956  69.965773889,-13.427959537  69.502351037,-13.771387507  69.039790315,-14.145406637  68.687433419,-14.490441666  68.440835791,-14.887272881  68.176801079,-15.199850053  67.925055055,-15.381273911  67.743741963,-15.539809351  67.553362203,-15.591544719  67.381894447,-15.348079034  67.338447774,-14.936077665  67.277714007,-14.46305655  67.21204519,-13.990903778  67.096233947,-13.54589758  66.966882597,-13.268923886  66.853540006,-12.821631959  66.680093502,-12.467434247  66.534149424,-12.267346945  66.42551068,-11.910599311  66.187157192,-11.767199321  66.047561153,-11.611181822  65.837857276,-11.453189531  65.552736547,-12.0333337783813  64.9000015258789,-10.4666662216187  65.0999984741211,-8.89999961853027  65.1666641235352,-7.03333330154419  64.8666687011719,-7.103168115  65.283694796))</t>
-  </si>
-  <si>
     <t>Faroe</t>
   </si>
   <si>
@@ -928,9 +922,6 @@
     <t>GS</t>
   </si>
   <si>
-    <t>POLYGON((-6.070436289  70.796587087,-6.482534667  70.877686691,-6.968045263  70.957275316,-7.329200449  71.01525725,-7.754596142  71.083122574,-8.283196925  71.153799736,-9.336997827  71.323403555,-10.543476003  71.485203733,-10.770921247  71.510746581,-10.550723259  71.765316178,-10.550723259  71.765316178,-10.361204118  71.992495126,-10.142397394  72.24962139,-9.92533692  72.467780947,-9.741228528  72.652811164,-9.494828604  72.965064819,-9.294028921  73.221165453,-9.155537543  73.368191888,-9.02616899  73.468268821,-8.835775523  73.544080869,-8.500203356  73.612516626,-8.258427496  73.660296347,-7.952277666  73.767075478,-7.574273348  73.894276457,-7.05432894  74.086796099,-6.546865885  74.277219974,-5.970870043  74.50716389,-5.360861181  74.737705597,-4.631983537  74.975532621,-4.144506801  75.143362945,7.752270412  75.340237441,7.975402441  75.06861306,8.184011982  74.910108507,8.40585101  74.747370237,8.631050445  74.585972628,8.773848069  74.443476101,8.827011983  74.298078517,8.76684331  74.104471322,8.623431125  73.927702414,8.383535587  73.773559199,8.019750502  73.563448151,7.788696112  73.44301858,7.423689393  73.338177245,6.766642418  73.22211733,6.121367426  73.062193149,5.596132545  72.97936504,4.883578177  72.891911925,3.748643142  72.69982499,2.945268203  72.578559283,2.001079927  72.415896356,1.46493148  72.323468392,0.883798041  72.2192928,0.141938058  72.069809872,-0.668928933  71.92670097,-1.592431116  71.748990349,-2.738903675  71.520165678,-3.293365895  71.401138856,-3.895005212  71.264388636,-4.350597262  71.162837942,-4.743731131  71.082796373,-5.274472302  70.963746041,-5.758260165  70.863037219,-6.070436289  70.796587087))</t>
-  </si>
-  <si>
     <t>IFF</t>
   </si>
   <si>
@@ -1007,13 +998,120 @@
   </si>
   <si>
     <t>solvae@hav.fo</t>
+  </si>
+  <si>
+    <t>POLYGON((5.072916666  63.141654839,5.324345937  63.27982073,5.764583334  63.651352689,5.580264779  63.748901887,5.871012258  64.08125,5.673693034  64.777859701,6.112449529  65.135416667,5.752158435  65.477083333,6.306249999  66.21252281,7.06875  66.601942223,8.008228204  66.81260513,8.927083334  67.329302251,10.239583332  68.009456131,12.09711365  68.623719685,11.8000001907349  68.8000030517578,11.1333332061768  68.6666641235352,9.86666679382324  68.4000015258789,8.86666679382324  67.9000015258789,8.60000038146973  67.9000015258789,8.30000019073486  67.7666702270508,7.76666688919067  67.9000015258789,7.30000019073486  68.2333297729492,6.46666669845581  68.2333297729492,5.76666688919067  68.2333297729492,5.23333311080933  68.4333343505859,4.56666660308838  68.2333297729492,3.83333325386047  68.3666687011719,3.20000004768372  68.3333358764648,1.96666669845581  67.8333358764648,1.515144101  67.800477996,1.5  67.466667175293,1.43333327770233  66.966667175293,1.79999995231628  66.5,2.29999995231628  66.1333312988281,2.06666660308838  65.966667175293,2.90000009536743  65.4333343505859,2.79999995231628  64.9000015258789,3.23333334922791  64.7666702270508,3.63333344459534  64.4333343505859,2.46666669845581  64.1333312988281,1.96666669845581  64.1666641235352,1.014696942  63.626922445,-0.533333361148834  63.4000015258789,-1.73333334922791  63.2666664123535,-2.36791519  63.040542854,2.7  62.5,5.072916666  63.141654839))</t>
+  </si>
+  <si>
+    <t>POLYGON((-7.103168115  65.283694796,-6.96666669845581  65.7666702270508,-7.40000009536743  66.0999984741211,-7.330920869  66.384246437,-7.63333320617676  67,-7.519915283  67.25104165,-7.643573575  67.771548904,-7.16666650772095  68.033332824707,-6.93333339691162  68.3666687011719,-7.40000009536743  68.6333312988281,-7.848642619  68.677507828,-7.628274775  68.88475312,-7.561650198  69.247807348,-7.46864723  69.504553404,-7.346337391  69.867374303,-7.167894825  70.118813088,-6.897805367  70.446951911,-6.618760544  70.650056588,-6.173734426  70.746620275,-6.070436289  70.796587087,-6.482534667  70.877686691,-6.968045263  70.957275316,-7.329200449  71.01525725,-7.754596142  71.083122574,-8.283196925  71.153799736,-9.336997827  71.323403555,-10.543476003  71.485203733,-10.770921247  71.510746581,-13.1  71.7,-18.4  67.381894447,-15.348079034  67.338447774,-14.936077665  67.277714007,-14.46305655  67.21204519,-13.990903778  67.096233947,-13.54589758  66.966882597,-13.268923886  66.853540006,-12.821631959  66.680093502,-12.467434247  66.534149424,-12.267346945  66.42551068,-11.910599311  66.187157192,-11.767199321  66.047561153,-11.611181822  65.837857276,-11.453189531  65.552736547,-12.0333337783813  64.9000015258789,-10.4666662216187  65.0999984741211,-8.89999961853027  65.1666641235352,-7.03333330154419  64.8666687011719,-7.103168115  65.283694796))</t>
+  </si>
+  <si>
+    <t>POLYGON((-6.070436289  70.796587087,-6.482534667  70.877686691,-6.968045263  70.957275316,-7.329200449  71.01525725,-7.754596142  71.083122574,-8.283196925  71.153799736,-9.336997827  71.323403555,-10.543476003  71.485203733,-10.770921247  71.510746581,-13.1  71.7,-8.835775523  73.544080869,-8.500203356  73.612516626,-8.258427496  73.660296347,-7.952277666  73.767075478,-7.574273348  73.894276457,-7.05432894  74.086796099,-6.546865885  74.277219974,-5.970870043  74.50716389,-5.360861181  74.737705597,-4.631983537  74.975532621,-4.144506801  75.143362945,7.752270412  75.340237441,7.975402441  75.06861306,8.184011982  74.910108507,8.40585101  74.747370237,8.631050445  74.585972628,8.773848069  74.443476101,8.827011983  74.298078517,8.76684331  74.104471322,8.623431125  73.927702414,8.383535587  73.773559199,8.019750502  73.563448151,7.788696112  73.44301858,7.423689393  73.338177245,6.766642418  73.22211733,6.121367426  73.062193149,5.596132545  72.97936504,4.883578177  72.891911925,3.748643142  72.69982499,2.945268203  72.578559283,2.001079927  72.415896356,1.46493148  72.323468392,0.883798041  72.2192928,0.141938058  72.069809872,-0.668928933  71.92670097,-1.592431116  71.748990349,-2.738903675  71.520165678,-3.293365895  71.401138856,-3.895005212  71.264388636,-4.350597262  71.162837942,-4.743731131  71.082796373,-5.274472302  70.963746041,-5.758260165  70.863037219,-6.070436289  70.796587087))</t>
+  </si>
+  <si>
+    <t>POLYGON((-28.5  60.5,-24.89999962  60.73333359,-24.23333359  60.76666641,-23.79999924  60.70000076,-23.5  60.53333282,-22.03333282  61.13333511,-21.33333397  61.20000076,-21.13333321  61.36666489,-21.26666641  61.53333282,-20.70000076  61.76666641,-20.20000076  61.66666794,-19.60000038  61.73333359,-18.96666718  61.66666794,-18.96666718  61.96666718,-18.66666603  61.96666718,-18.06666756  61.86666489,-17.63333321  62.06666565,-17.53333282  62.33333206,-17  62.59999847,-16.63333321  62.5,-15.5666666  62.63333511,-15.26666641  62.73333359,-14.76666641  61.76666641,-14.39999962  61.5,-14.60000038  61.29999924,-15  60.23333359,-15.66666698  59.96666718,-16.06666756  59.79999924,-16.56666756  59.83333206,-18.13333321  59.40000153,-19.46666718  58.79999924,-19.79999924  58.53333282,-20.73333359  57.16666794,-21.03333282  57.06666565,-22.10000038  56.46666718,-22.56666756  56.40000153,-23.16666603  55.93333435,-23.29999924  55.79999924,-22.46666718  55.43333435,-21.86666679  55.43333435,-20.86666679  55.59999847,-20.13333321  55.16666794,-20.29999924  55.03333282,-20.16666603  53.76666641,-19.86666679  53.70000076,-18.66666603  54.13333511,-18.13333321  54.29999924,-17.66666603  54.5,-17.33333397  54.56666565,-16.53333282  55.06666565,-15.73333359  55.23333359,-15.03333378  55.53333282,-14.16666698  56,-12.86666679  57,-11.73333359  57.23333359,-11.53333378  57.59999847,-11.16666698  58,-10.66666698  58.23333359,-10.0666666  58.09999847,-9.533333778  58.20000076,-8.800000191  58.29999924,-8.333333015  58.36666489,-7.699999809  58.66666794,-7.300000191  59.03333282,-7.033333302  59.16666794,-6.533333302  59.33333206,-6.066666603  59.63333511,-5.433333397  59.73333359,-4.933333397  59.90000153,-4.366666794  60.09999847,-3.799999952  60.33333206,-3.333333254  60.33333206,-3.133333445  60.43333435,-2.433333397  60.83333206,-0.699999988  61.59999847,-0.300000012  61.63333511,0.13333334  61.73333359,0.699999988  61.59999847,1.166666627  61.70000076,2.7  62.5,-2.36791519  63.04054285,-3.200000048  63.13333511,-4.081391907  62.97646006,-5.766666889  63.06666565,-5.833333492  63.26666641,-5.937494755  62.6875,-5.766666889  62.66666794,-5.633333206  62.59999847,-5.433333397  62.56666565,-5.099999905  62.5,-4.833333492  62.29999924,-4.633333206  62.23333359,-4.5  62,-4.800000191  61.93333435,-4.866666794  61.93333435,-5.033333302  61.79999924,-4.966666698  61.66666794,-5.066666603  61.63333511,-5.233333111  61.56666565,-5.233333111  61.46666718,-5.300000191  61.43333435,-5.566666603  61.36666489,-5.566666603  61.26666641,-5.800000191  61.16666794,-5.900000095  60.96666718,-6.099999905  60.90000153,-6.233333111  60.76666641,-6.199999809  60.66666794,-6.366666794  60.63333511,-6.533333302  60.70000076,-6.633333206  60.76666641,-6.833333492  60.79999924,-7.066666603  61.20000076,-7.099999905  61.26666641,-7.233333111  61.29999924,-7.266666889  61.36666489,-7.533333302  61.40000153,-7.566666603  61.46666718,-7.699999809  61.46666718,-7.933333397  61.46666718,-8  61.5,-8  61.53333282,-7.800000191  61.63333511,-7.833333492  61.73333359,-8.100000381  61.59999847,-8.166666985  61.63333511,-8.233333588  61.73333359,-8.333333015  61.79999924,-8.5  62.20000076,-8.433333397  62.29999924,-8.033333778  62.56666565,-7.666666508  62.63333511,-7.433333397  62.70000076,-7  62.73333359,-6.687494755  62.77083206,-6.533333302  62.73333359,-6.366666794  62.73333359,-6.133333206  62.70000076,-5.937494755  62.6875,-5.833333492  63.26666641,-7.354161739  63.6875,-8.399999619  63.93333435,-10.26666641  64.03333282,-11.47916126  64.52083588,-12.53333378  64.43333435,-12.73333359  64.23332977,-14.26666641  63.73333359,-15.4333334  63.46666718,-16.23333359  63.33333206,-17.63333321  63.29999924,-18.89999962  63.26666641,-19.70000076  63.36666489,-20.23333359  63.23333359,-21.93333244  63.33333206,-22.46666718  63.66666794,-23.06666756  63.29999924,-28.5  60.5))</t>
+  </si>
+  <si>
+    <t>WGINORAWS</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>StrataFullName</t>
+  </si>
+  <si>
+    <t>StrateDescription</t>
+  </si>
+  <si>
+    <t>Atlantic water that has just entered the Norwegian Sea</t>
+  </si>
+  <si>
+    <t>Atlantic Water</t>
+  </si>
+  <si>
+    <t>Atlantic Water South</t>
+  </si>
+  <si>
+    <t>Atlantic water on it’s way to enter the Norwegian Sea</t>
+  </si>
+  <si>
+    <t>East Icelandic Water</t>
+  </si>
+  <si>
+    <t>The area north/Northwest of the Icelandic Shelf, west of the Kolbeinsey Ridge, stretching northwards up to Jan Mayen and east/southeast towards the frontal zones (Polar front/IFF front).</t>
+  </si>
+  <si>
+    <t>Faroes</t>
+  </si>
+  <si>
+    <t>Faroe Shelf Water</t>
+  </si>
+  <si>
+    <t>Greenland Sea</t>
+  </si>
+  <si>
+    <t>The area east of Greenland Shelf and north of Jan Mayen out to the Mohn’s Ridge. Contains the nortwestern most part of the area surveyed in the International Ecosystem summer surveys.</t>
+  </si>
+  <si>
+    <t>Iceland-Faroe Front</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Iceland-Faroes frontal zone. This polygon should be thought of as an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>area to be excluded,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when computing averages, since it contains a mix of several watermasses.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lofoten Basin East</t>
+  </si>
+  <si>
+    <t>The eastern part of the Lofoten Basin.</t>
+  </si>
+  <si>
+    <t>The western part of the Lofoten Basin.</t>
+  </si>
+  <si>
+    <t>Lofoten Basin West</t>
+  </si>
+  <si>
+    <t>Norwegian Sea East</t>
+  </si>
+  <si>
+    <t>The eastern part of the Norwegian Sea.</t>
+  </si>
+  <si>
+    <t>Norwegian Sea West</t>
+  </si>
+  <si>
+    <t>The wester part of the Norwegian Sea.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1031,6 +1129,21 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1057,17 +1170,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1387,7 +1505,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1441,7 +1559,7 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -1577,25 +1695,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C8">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H8" t="s">
         <v>7</v>
@@ -1610,7 +1728,7 @@
     <hyperlink ref="H5" r:id="rId5" xr:uid="{DF03A206-DD44-134D-8758-A4C618F52FB8}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{FFF0153F-B882-3B49-B8E4-BB58C9D1D88D}"/>
     <hyperlink ref="G7" r:id="rId7" xr:uid="{94CFEBA0-3D40-4D42-A7BB-53A23AFF94FC}"/>
-    <hyperlink ref="G8" r:id="rId8" xr:uid="{279863F1-76F1-2147-9B40-A943E1E0AD1F}"/>
+    <hyperlink ref="G8" r:id="rId8" xr:uid="{31F5C149-3CE6-5F4A-8A2F-EF733C2532FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1618,1139 +1736,1220 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D5741E-99AC-B447-A885-CE0B145669F3}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.1640625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="D1" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="A35" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="A36" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="B36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="B37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="A38" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="B38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="B40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="A41" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="B41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="A42" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B42" t="s">
-        <v>32</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="B42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B44" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="A45" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B45" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="A46" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="B46" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="A47" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B47" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="A48" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="B48" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="A49" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="B49" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="A50" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="B50" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="A51" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="B51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="A52" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="B52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="A53" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="A54" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B54" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="B54" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="A55" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="A56" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B56" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="B56" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="A57" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B57" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="3" t="s">
+      <c r="B57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="A58" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B58" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="B58" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="A59" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="B59" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="A60" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B60" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="3" t="s">
+      <c r="B60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="A61" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B61" t="s">
-        <v>32</v>
-      </c>
-      <c r="C61" s="3" t="s">
+      <c r="B61" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="A62" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B62" t="s">
-        <v>32</v>
-      </c>
-      <c r="C62" s="3" t="s">
+      <c r="B62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="A63" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B63" t="s">
-        <v>32</v>
-      </c>
-      <c r="C63" s="3" t="s">
+      <c r="B63" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="A64" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B64" t="s">
-        <v>32</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="B64" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="A65" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B65" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="B65" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="A66" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="B66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="A67" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B67" t="s">
-        <v>32</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="B67" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="A68" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B68" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="B68" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="A69" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="3" t="s">
+      <c r="B69" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="A70" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="3" t="s">
+      <c r="B70" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="A71" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="B71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="A72" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B72" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="B72" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="A73" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B73" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="B73" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="A74" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B74" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="B74" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="A75" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B75" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="B75" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="A76" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B76" t="s">
-        <v>32</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="B76" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="A77" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B77" t="s">
-        <v>32</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="B77" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="A78" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B78" t="s">
-        <v>32</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="B78" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="A79" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B79" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="B79" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="A80" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B80" t="s">
-        <v>32</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="B80" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B81" t="s">
-        <v>32</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="B81" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B82" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="3" t="s">
+      <c r="B82" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B83" t="s">
-        <v>32</v>
-      </c>
-      <c r="C83" s="3" t="s">
+      <c r="B83" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B84" t="s">
-        <v>32</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="B84" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B85" t="s">
-        <v>32</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="B85" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B86" t="s">
-        <v>32</v>
-      </c>
-      <c r="C86" s="3" t="s">
+      <c r="B86" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B87" t="s">
-        <v>32</v>
-      </c>
-      <c r="C87" s="3" t="s">
+      <c r="B87" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B88" t="s">
-        <v>32</v>
-      </c>
-      <c r="C88" s="3" t="s">
+      <c r="B88" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B89" t="s">
-        <v>32</v>
-      </c>
-      <c r="C89" s="3" t="s">
+      <c r="B89" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C90" s="3" t="s">
+      <c r="B90" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B91" t="s">
-        <v>32</v>
-      </c>
-      <c r="C91" s="3" t="s">
+      <c r="B91" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B92" t="s">
-        <v>32</v>
-      </c>
-      <c r="C92" s="3" t="s">
+      <c r="B92" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B93" t="s">
-        <v>319</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="B97" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B94" t="s">
-        <v>319</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="B98" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B95" t="s">
-        <v>319</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="B99" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B96" t="s">
-        <v>319</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="B100" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B97" t="s">
-        <v>319</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="B101" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B98" t="s">
-        <v>319</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+      <c r="B102" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B99" t="s">
-        <v>319</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="B103" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B100" t="s">
-        <v>319</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>317</v>
-      </c>
-      <c r="B101" t="s">
-        <v>319</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>318</v>
-      </c>
-      <c r="B102" t="s">
-        <v>319</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>307</v>
+      <c r="C103" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2794,7 +2993,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E57A2BD-8BAD-D140-8A4E-30FC2DECDAD9}">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
@@ -3539,82 +3738,90 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B95" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B96" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B97" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B98" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B100" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B102" t="s">
-        <v>308</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>315</v>
+      </c>
+      <c r="B103" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
